--- a/files/me-ADPER9000006488.xlsx
+++ b/files/me-ADPER9000006488.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M10"/>
+  <dimension ref="A1:M12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -553,7 +553,7 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>세 학회지</t>
+          <t>수집 학회지</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -573,45 +573,45 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>농업용 저수지의 가능최대홍수량 설계를 위한 하류부 피해 산정 방안 적용성 분석</t>
+          <t>Development and utilization of agricultural and rural climate information systems to respond to climate crisis</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>주동혁, 나라, 김하영, 소의건, 송인홍, 이성학, 신길채, 심규현, 허건, 유승환</t>
+          <t>Hayoung Kim, 나라, Dong-Hyuk Joo, Euigeon So, Seung-Hwan Yoo, Seung-Jong Bae, Soo-Jin Kim, Yeong-cheol Kwak, ByeongWoo Choi, K. Park, DalJu Park, YunPyo Lee, MyungWon Lee, YongDuk Shin</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>한국농공학회논문집</t>
+          <t>한국기후변화학회지</t>
         </is>
       </c>
       <c r="F3" s="2" t="n">
-        <v>67</v>
+        <v>16</v>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5-2</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>59-70</t>
+          <t>1129-1139</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>10.5389/KSAE.2025.67.3.059</t>
+          <t>10.15531/ksccr.2025.16.5.1129</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>세 학회지</t>
+          <t>수집 학회지</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>공저자</t>
+          <t>주저자</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr"/>
@@ -622,16 +622,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>K-HAS와 비율보정 계수를 이용한 농업용 저수지의 비상연계 용수공급 가능량 분석</t>
+          <t>농업용 저수지의 가능최대홍수량 설계를 위한 하류부 피해 산정 방안 적용성 분석</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>김하영, 이상현, 나라, 주동혁, 유승환</t>
+          <t>주동혁, 나라, 김하영, 소의건, 송인홍, 이성학, 신길채, 심규현, 허건, 유승환</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -640,31 +640,31 @@
         </is>
       </c>
       <c r="F4" s="2" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>59-71</t>
+          <t>59-70</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10.5389/KSAE.2023.65.2.059</t>
+          <t>10.5389/KSAE.2025.67.3.059</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>세 학회지</t>
+          <t>수집 학회지</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>주저자</t>
+          <t>공저자</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr"/>
@@ -675,44 +675,44 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>농업용 수로부의 수위 보정을 위한 필터기법별 적용성 분석</t>
+          <t>Development of a future weather database based on Shared Socioeconomic Pathways scenarios for assessing climate change vulnerability of agricultural infrastructure</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>주동혁, 나라, 김하영, 최규훈, 윤형창, 박상빈, 유승환</t>
+          <t>Dong-Hyuk Joo, 나라, Ha-Young Kim, Jaepil Cho, JuHyoung Lee, Suk-ho Song, DalJu Park, , YunPyo Lee, MyoungWon Lee, Seung-Hwan Yoo</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>한국농공학회논문집</t>
+          <t>한국기후변화학회지</t>
         </is>
       </c>
       <c r="F5" s="2" t="n">
-        <v>65</v>
+        <v>15</v>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5-2</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>51-68</t>
+          <t>953-964</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10.5389/KSAE.2023.65.5.051</t>
+          <t>10.15531/ksccr.2024.15.5.953</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>세 학회지</t>
+          <t>수집 학회지</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -732,12 +732,12 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>딥러닝 기법을 이용한 농업용저수지 CCTV 영상 기반의 수위계측 방법 개발</t>
+          <t>K-HAS와 비율보정 계수를 이용한 농업용 저수지의 비상연계 용수공급 가능량 분석</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>주동혁, 이상현, 최규훈, 유승환, 나라, 김하영, 오창조, 윤광식</t>
+          <t>김하영, 이상현, 나라, 주동혁, 유승환</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -750,27 +750,27 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>15-26</t>
+          <t>59-71</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>10.5389/KSAE.2023.65.1.015</t>
+          <t>10.5389/KSAE.2023.65.2.059</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>세 학회지</t>
+          <t>수집 학회지</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>공저자</t>
+          <t>주저자</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr"/>
@@ -785,40 +785,40 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>물-에너지-식량-탄소 넥서스를 이용한 통합물관리 모델 평가 연구 - 영산강 수계를 중심으로 -</t>
+          <t>농업용 수로부의 수위 보정을 위한 필터기법별 적용성 분석</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>나라, 박진현, 주동혁, 김하영, 유승환, 오창조, 이상현, 오부영, 허승오</t>
+          <t>주동혁, 나라, 김하영, 최규훈, 윤형창, 박상빈, 유승환</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>농촌계획</t>
+          <t>한국농공학회논문집</t>
         </is>
       </c>
       <c r="F7" s="2" t="n">
-        <v>29</v>
+        <v>65</v>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>37-49</t>
+          <t>51-68</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10.7851/ksrp.2023.29.1.037</t>
+          <t>10.5389/KSAE.2023.65.5.051</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>세 학회지</t>
+          <t>수집 학회지</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -834,49 +834,49 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>YOLO v2를 이용한 고해상도 항공영상에서의 태양광발전소 탐지 방법 연구</t>
+          <t>딥러닝 기법을 이용한 농업용저수지 CCTV 영상 기반의 수위계측 방법 개발</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>김하영, 나라, 주동혁, 최규훈, 오윤경</t>
+          <t>주동혁, 이상현, 최규훈, 유승환, 나라, 김하영, 오창조, 윤광식</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>농촌계획</t>
+          <t>한국농공학회논문집</t>
         </is>
       </c>
       <c r="F8" s="2" t="n">
-        <v>28</v>
+        <v>65</v>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>87-96</t>
+          <t>15-26</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>10.7851/ksrp.2022.28.2.087</t>
+          <t>10.5389/KSAE.2023.65.1.015</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>세 학회지</t>
+          <t>수집 학회지</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>주저자</t>
+          <t>공저자</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr"/>
@@ -887,16 +887,16 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>농업경영체 등록정보와 공간정보를 활용한 농지범용화 사업 대상지 선정 방안 개발 및 적용</t>
+          <t>물-에너지-식량-탄소 넥서스를 이용한 통합물관리 모델 평가 연구 - 영산강 수계를 중심으로 -</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>나라, 주동혁, 김하영, 유승환, 곽영철, 김정훈, 이향미, 조은정</t>
+          <t>나라, 박진현, 주동혁, 김하영, 유승환, 오창조, 이상현, 오부영, 허승오</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -905,7 +905,7 @@
         </is>
       </c>
       <c r="F9" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
@@ -914,17 +914,17 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>17-26</t>
+          <t>37-49</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10.7851/ksrp.2022.28.1.017</t>
+          <t>10.7851/ksrp.2023.29.1.037</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>세 학회지</t>
+          <t>수집 학회지</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -944,49 +944,155 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>농업용저수지의 실시간 수위 보정을 위한 Hampel Filter의 최적 Window Size 분석</t>
+          <t>YOLO v2를 이용한 고해상도 항공영상에서의 태양광발전소 탐지 방법 연구</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>주동혁, 나라, 김하영, 최규훈, 권재환, 유승환</t>
+          <t>김하영, 나라, 주동혁, 최규훈, 오윤경</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>한국농공학회논문집</t>
+          <t>농촌계획</t>
         </is>
       </c>
       <c r="F10" s="2" t="n">
-        <v>64</v>
+        <v>28</v>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9-24</t>
+          <t>87-96</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10.5389/KSAE.2022.64.3.009</t>
+          <t>10.7851/ksrp.2022.28.2.087</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>세 학회지</t>
+          <t>수집 학회지</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>공저자</t>
+          <t>주저자</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr"/>
       <c r="M10" s="2" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>농업경영체 등록정보와 공간정보를 활용한 농지범용화 사업 대상지 선정 방안 개발 및 적용</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>나라, 주동혁, 김하영, 유승환, 곽영철, 김정훈, 이향미, 조은정</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>농촌계획</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>17-26</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>10.7851/ksrp.2022.28.1.017</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>수집 학회지</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>공저자</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr"/>
+      <c r="M11" s="2" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>농업용저수지의 실시간 수위 보정을 위한 Hampel Filter의 최적 Window Size 분석</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>주동혁, 나라, 김하영, 최규훈, 권재환, 유승환</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>한국농공학회논문집</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>64</v>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>9-24</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>10.5389/KSAE.2022.64.3.009</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>수집 학회지</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>공저자</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr"/>
+      <c r="M12" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
